--- a/_historico/coleta_bruta/FNDE_output.xlsx
+++ b/_historico/coleta_bruta/FNDE_output.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FNDE_output" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FNDE_output'!$A$1:$P$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FNDE_output'!$A$1:$P$124</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P102"/>
+  <dimension ref="A1:P124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6838,8 +6838,1376 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>1098</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>VASSOURA DE CERDAS DURAS - PARA ESFREGAR PISOS.</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>PREVEOESTE MATERIAIS DE SEGURANCA E DESCARTAVEIS LTDA (PreveOeste)</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>01.974.824/0001-25</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>https://www.preveoeste.com.br/vassoura-super-tupy-cerdas-longas-com-cabo-120mt-2075-p140926</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>Vassoura Super Tupy Cerdas Longas Com Cabo 1,20mt</t>
+        </is>
+      </c>
+      <c r="J103" s="5" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="K103" s="2" t="n"/>
+      <c r="L103" s="2" t="n"/>
+      <c r="M103" s="5" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="N103" s="5" t="n">
+        <v>22.76</v>
+      </c>
+      <c r="O103" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: JadLog R$ 22,76 5 dia(s) útil(eis)</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>VASSOURA DE PELO SINTÉTICO – 60 CM - PARA LIMPEZA GERAL.</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>58.509.800/0001-12</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="n"/>
+      <c r="I104" s="3" t="inlineStr">
+        <is>
+          <t>Vassoura pelo 60cm Plástica Sintética 50 S/Cabo - DSR</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="n"/>
+      <c r="K104" s="2" t="n"/>
+      <c r="L104" s="2" t="n"/>
+      <c r="M104" s="2" t="n"/>
+      <c r="N104" s="2" t="n"/>
+      <c r="O104" s="3" t="inlineStr">
+        <is>
+          <t>Preço não exibido (motivo não identificado)</t>
+        </is>
+      </c>
+      <c r="P104" s="4" t="inlineStr">
+        <is>
+          <t>https://www.starsprodutosdelimpeza.com.br/vassoura-pelo-60cm-plastica-sintetica-scabo-dsr</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>1103</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>VASSOURA DE TETO/VASCULHO - CERDAS DE NYLON; CABO LONGO.</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>PREVEOESTE MATERIAIS DE SEGURANCA E DESCARTAVEIS LTDA (PreveOeste)</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>01.974.824/0001-25</t>
+        </is>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>https://www.preveoeste.com.br/vassoura-tira-po-limpa-teto-forro-e-gesso-1982-p140450</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>Vassoura Tira Pó Limpa Teto Forro e Gesso</t>
+        </is>
+      </c>
+      <c r="J105" s="5" t="n">
+        <v>25.55</v>
+      </c>
+      <c r="K105" s="2" t="n"/>
+      <c r="L105" s="2" t="n"/>
+      <c r="M105" s="5" t="n">
+        <v>25.55</v>
+      </c>
+      <c r="N105" s="5" t="n">
+        <v>21.62</v>
+      </c>
+      <c r="O105" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: JadLog R$ 21,62 5 dia(s) útil(eis)</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>LIMPEZA PREDIAL</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>1103</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>VASSOURA DE TETO/VASCULHO - CERDAS DE NYLON; CABO LONGO.</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>J. F. DE MEDEIROS LTDA (Stars Produtos de Limpeza)</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>58.509.800/0001-12</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="n"/>
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t>Vassoura Limpa Teto Nylon Bola c/Cabo 2,20mt</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="n"/>
+      <c r="K106" s="2" t="n"/>
+      <c r="L106" s="2" t="n"/>
+      <c r="M106" s="2" t="n"/>
+      <c r="N106" s="2" t="n"/>
+      <c r="O106" s="3" t="inlineStr">
+        <is>
+          <t>Preço não exibido (motivo não identificado)</t>
+        </is>
+      </c>
+      <c r="P106" s="4" t="inlineStr">
+        <is>
+          <t>https://www.starsprodutosdelimpeza.com.br/vassoura-limpa-teto-especial-c-cabo-madeira</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>1104</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>CAMISETA/CAMISA DE UNIFORME - MALHA FRIA, GOLA REDONDA/ESPORTE, IDENTIFICAÇÃO DA EMPRESA; DEFINIR MANGA CURTA/LONGA CONFORME POSTO.</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>27.061.442/0002-85</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>https://www.lojas360.com.br/uniforme/camisa-azul-royal-manga-longa-em-brim-com-gola-italiana-e-refletivo?variant_id=4211</t>
+        </is>
+      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>Camisa Azul Royal Manga Longa em Brim com Gola Italiana e Refletivo</t>
+        </is>
+      </c>
+      <c r="J107" s="5" t="n">
+        <v>90.23999999999999</v>
+      </c>
+      <c r="K107" s="2" t="n"/>
+      <c r="L107" s="2" t="n"/>
+      <c r="M107" s="5" t="n">
+        <v>90.23999999999999</v>
+      </c>
+      <c r="N107" s="5" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="O107" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: PAC R$ 18,40 Até 10 dias úteis após o faturamento do pedido.rn</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>1104</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>CAMISETA/CAMISA DE UNIFORME - MALHA FRIA, GOLA REDONDA/ESPORTE, IDENTIFICAÇÃO DA EMPRESA; DEFINIR MANGA CURTA/LONGA CONFORME POSTO.</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>COMERCIAL DE REFRIGERACAO PANAN OESTE LTDA (Panan)</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>15.448.996/0001-70</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>https://www.panan.com.br/pecas-e-epi/avental-e-camiseta/camiseta-profissional-branca-gg-para-cozinha-e-trabalho-em-poliester</t>
+        </is>
+      </c>
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t>Camiseta Profissional Branca GG para Cozinha e Trabalho em Poliéster.</t>
+        </is>
+      </c>
+      <c r="J108" s="5" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="K108" s="2" t="n"/>
+      <c r="L108" s="2" t="n"/>
+      <c r="M108" s="5" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="N108" s="5" t="n">
+        <v>73.09</v>
+      </c>
+      <c r="O108" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Correios Econômico R$ 73,09 7 a 9 dias úteis</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>1104</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>CAMISETA/CAMISA DE UNIFORME - MALHA FRIA, GOLA REDONDA/ESPORTE, IDENTIFICAÇÃO DA EMPRESA; DEFINIR MANGA CURTA/LONGA CONFORME POSTO.</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>LIVPRO LTDA</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>60.147.971/0001-90</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="n"/>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>Camiseta Masculina Malha PV Gola Redonda</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="n"/>
+      <c r="K109" s="2" t="n"/>
+      <c r="L109" s="2" t="n"/>
+      <c r="M109" s="2" t="n"/>
+      <c r="N109" s="2" t="n"/>
+      <c r="O109" s="3" t="inlineStr">
+        <is>
+          <t>Preço não exibido (motivo não identificado)</t>
+        </is>
+      </c>
+      <c r="P109" s="4" t="inlineStr">
+        <is>
+          <t>https://livpro.com.br/products/camiseta-masculina-malha-pv-gola-redonda?Cor=Azul-marinho&amp;Desenho+do+tecido=Lisa&amp;Tamanho=P</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>CALÇA DE UNIFORME - TECIDO RESISTENTE (BRIM OU EQUIVALENTE), BOLSOS E FECHAMENTO FRONTAL.</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>27.061.442/0002-85</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>https://www.lojas360.com.br/uniforme/calca-em-brim-azul-royal-com-elastico-total-e-refletivo?variant_id=4175</t>
+        </is>
+      </c>
+      <c r="I110" s="3" t="inlineStr">
+        <is>
+          <t>Calça em Brim Azul Royal com Elástico total e Refletivo</t>
+        </is>
+      </c>
+      <c r="J110" s="5" t="n">
+        <v>78.42</v>
+      </c>
+      <c r="K110" s="2" t="n"/>
+      <c r="L110" s="2" t="n"/>
+      <c r="M110" s="5" t="n">
+        <v>78.42</v>
+      </c>
+      <c r="N110" s="5" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="O110" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: PAC R$ 18,40 Até 10 dias úteis após o faturamento do pedido.rn</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>CALÇA DE UNIFORME - TECIDO RESISTENTE (BRIM OU EQUIVALENTE), BOLSOS E FECHAMENTO FRONTAL.</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>LIVPRO LTDA</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>60.147.971/0001-90</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="n"/>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>Calça Masculina Brim Elástico Total 100% Algodão</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="n"/>
+      <c r="K111" s="2" t="n"/>
+      <c r="L111" s="2" t="n"/>
+      <c r="M111" s="2" t="n"/>
+      <c r="N111" s="2" t="n"/>
+      <c r="O111" s="3" t="inlineStr">
+        <is>
+          <t>Preço não exibido (motivo não identificado)</t>
+        </is>
+      </c>
+      <c r="P111" s="4" t="inlineStr">
+        <is>
+          <t>https://livpro.com.br/products/calca-de-trabalho-elastico-total-algodao?Cor=Azul-marinho&amp;Desenho+do+tecido=Lisa&amp;Tamanho=P</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>MEIA - ALGODÃO/POLIAMIDA/ELASTANO; COR PRETA OU AZUL.</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>SEGURANCA TOTAL EPIS LTDA</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>39.268.527/0001-37</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>https://www.segurancatotal.com.br/meiao-futebol-treino-profissional-algodao</t>
+        </is>
+      </c>
+      <c r="I112" s="3" t="inlineStr">
+        <is>
+          <t>Meião Futebol Treino Profissional Algodão</t>
+        </is>
+      </c>
+      <c r="J112" s="5" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="K112" s="2" t="n"/>
+      <c r="L112" s="2" t="n"/>
+      <c r="M112" s="5" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="N112" s="5" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="O112" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC</t>
+        </is>
+      </c>
+      <c r="P112" s="2" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>MEIA - ALGODÃO/POLIAMIDA/ELASTANO; COR PRETA OU AZUL.</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>TR Distribuidora de Equipamentos de Segurança LTDA</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>14.213.841/0001-91</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>https://www.trepis.com.br/c-a-41555-meiao-de-algodao-cru-modelo-tubular-atoalhado-riscos-termicos-frio</t>
+        </is>
+      </c>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>Meião de Algodão Cru Térmico Tubular Atoalhado CA 41555</t>
+        </is>
+      </c>
+      <c r="J113" s="5" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="K113" s="2" t="n"/>
+      <c r="L113" s="2" t="n"/>
+      <c r="M113" s="5" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="N113" s="5" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="O113" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: JADLOG .Package R$ 21,55 Capital de todo Brasil: 01 a 03 dias. Interior de Todo Brasil: 02 a 05 dias.</t>
+        </is>
+      </c>
+      <c r="P113" s="2" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>CALÇADO DE SEGURANÇA ANTIDERRAPANTE - PROTEÇÃO CONTRA AGENTES MECÂNICOS; IMPERMEÁVEL QUANDO APLICÁVEL.</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>A MASTER ARTIGOS PARA PROTECAO INDIVIDUAL E INDUSTRIAL LTDA (A Master EPI)</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>16.603.654/0001-40</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="n"/>
+      <c r="I114" s="3" t="n"/>
+      <c r="J114" s="2" t="n"/>
+      <c r="K114" s="2" t="n"/>
+      <c r="L114" s="2" t="n"/>
+      <c r="M114" s="2" t="n"/>
+      <c r="N114" s="2" t="n"/>
+      <c r="O114" s="3" t="inlineStr">
+        <is>
+          <t>Preço não exibido (motivo não identificado)</t>
+        </is>
+      </c>
+      <c r="P114" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amasterepi.com.br/busca?q=Cal%C3%A7ado%20De%20Seguran%C3%A7a%20Antiderrapante</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>1109</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>LUVA DE PVC - CANO MÉDIO OU LONGO; PARA ATIVIDADES DE LIMPEZA.</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>SEGURANCA TOTAL EPIS LTDA</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>39.268.527/0001-37</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>https://www.segurancatotal.com.br/luva-de-pvc-forrada-palma-aspera-plastcor-45cm-ca-34570</t>
+        </is>
+      </c>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>LUVA PVC HANDEX PALMA ASPERA 46CM</t>
+        </is>
+      </c>
+      <c r="J115" s="5" t="n">
+        <v>26.78</v>
+      </c>
+      <c r="K115" s="2" t="n"/>
+      <c r="L115" s="2" t="n"/>
+      <c r="M115" s="5" t="n">
+        <v>26.78</v>
+      </c>
+      <c r="N115" s="5" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="O115" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC</t>
+        </is>
+      </c>
+      <c r="P115" s="2" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>1110</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>LUVA DE LÁTEX FORRADA - CANO CURTO; TAMANHOS VARIADOS.</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>SEGURANCA TOTAL EPIS LTDA</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>39.268.527/0001-37</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>https://www.segurancatotal.com.br/luva-de-latex-kalipso-amarela-ca-13959</t>
+        </is>
+      </c>
+      <c r="I116" s="3" t="inlineStr">
+        <is>
+          <t>Luva de Látex Multiuso Kalipso Amarela CA13959 (Tamanho: P)</t>
+        </is>
+      </c>
+      <c r="J116" s="5" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="K116" s="2" t="n"/>
+      <c r="L116" s="2" t="n"/>
+      <c r="M116" s="5" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="N116" s="5" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="O116" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>1112</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>LUVA DE ALGODÃO PIGMENTADA - PARA ATIVIDADES DE APOIO/MANUSEIO.</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>BHZ EPI DISTRIBUIDORA LTDA</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>31.893.116/0001-20</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>https://www.loja.bhzepi.com.br/luva-de-segurana-malha-tricotada-pigmentada-branca</t>
+        </is>
+      </c>
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t>Luva De Segurança Malha Tricotada Pigmentada branca</t>
+        </is>
+      </c>
+      <c r="J117" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K117" s="2" t="n"/>
+      <c r="L117" s="2" t="n"/>
+      <c r="M117" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N117" s="5" t="n">
+        <v>20.62</v>
+      </c>
+      <c r="O117" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 20,62 7 dias úteis PAC</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>1112</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>LUVA DE ALGODÃO PIGMENTADA - PARA ATIVIDADES DE APOIO/MANUSEIO.</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>27.061.442/0002-85</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>https://www.lojas360.com.br/luvas-de-seguranca/luva-tricotada-cru-com-6-fios-pigmentada-branca-c-a-31909</t>
+        </is>
+      </c>
+      <c r="I118" s="3" t="inlineStr">
+        <is>
+          <t>Luva Tricotada Cru Com 6 Fios Pigmentada Branca | C.A. 31909</t>
+        </is>
+      </c>
+      <c r="J118" s="5" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="K118" s="2" t="n"/>
+      <c r="L118" s="2" t="n"/>
+      <c r="M118" s="5" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="N118" s="5" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="O118" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: PAC R$ 18,40 Até 10 dias úteis após o faturamento do pedido.rn</t>
+        </is>
+      </c>
+      <c r="P118" s="2" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>1113</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>ÓCULOS DE PROTEÇÃO INCOLOR - PARA MANIPULAÇÃO E APLICAÇÃO DE PRODUTOS QUÍMICOS.</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>SINGULAR COMERCIO DE EQUIPAMENTOS DE PROTECAO INDIVIDUAL LTDA (Loja do EPI)</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>20.838.307/0001-73</t>
+        </is>
+      </c>
+      <c r="H119" s="4" t="inlineStr">
+        <is>
+          <t>https://www.lojadoepi.com.br/oculos-de-protecao-vvision-600-incolor-antiembacante-volk-ca-42922-p3187</t>
+        </is>
+      </c>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t>Óculos de Proteção Vvision 600 Incolor Antiembaçante Volk CA 42922</t>
+        </is>
+      </c>
+      <c r="J119" s="5" t="n">
+        <v>26.93</v>
+      </c>
+      <c r="K119" s="2" t="n"/>
+      <c r="L119" s="2" t="n"/>
+      <c r="M119" s="5" t="n">
+        <v>26.93</v>
+      </c>
+      <c r="N119" s="5" t="n">
+        <v>21.39</v>
+      </c>
+      <c r="O119" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Pac R$ 21,39 7 dia(s) útil(eis)</t>
+        </is>
+      </c>
+      <c r="P119" s="2" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>1114</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>MÁSCARA DE PROTEÇÃO DESCARTÁVEL - USO CONFORME RISCO/ATIVIDADE.</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>ASTRO DISTRIBUIDORA LTDA</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>18.597.685/0001-60</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>https://www.astrodistribuidora.com/mascara-de-tnt-descartavel-com-elastico-volk</t>
+        </is>
+      </c>
+      <c r="I120" s="3" t="inlineStr">
+        <is>
+          <t>Máscara de TNT Descartável com Elástico - Volk (100 Unidades)</t>
+        </is>
+      </c>
+      <c r="J120" s="5" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="K120" s="2" t="n"/>
+      <c r="L120" s="2" t="n"/>
+      <c r="M120" s="5" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="N120" s="5" t="n">
+        <v>26.82</v>
+      </c>
+      <c r="O120" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: JADLOG - Entrega em até 5 dias úteis - R$26,82 BRASPRESS - Entrega em até 15 dias úteis -</t>
+        </is>
+      </c>
+      <c r="P120" s="2" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>1114</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>MÁSCARA DE PROTEÇÃO DESCARTÁVEL - USO CONFORME RISCO/ATIVIDADE.</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>TR Distribuidora de Equipamentos de Segurança LTDA</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>14.213.841/0001-91</t>
+        </is>
+      </c>
+      <c r="H121" s="4" t="inlineStr">
+        <is>
+          <t>https://www.trepis.com.br/mascara-descartavel-confec-em-tnt-tripla-branca-com-elastico-pct-c50un</t>
+        </is>
+      </c>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>Máscara Descartável Tripla TNT Branca com Elástico Pacote com 50 Unidades</t>
+        </is>
+      </c>
+      <c r="J121" s="5" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="K121" s="2" t="n"/>
+      <c r="L121" s="2" t="n"/>
+      <c r="M121" s="5" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="N121" s="5" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="O121" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: JADLOG .Package R$ 21,55 Capital de todo Brasil: 01 a 03 dias. Interior de Todo Brasil: 02 a 05 dias.</t>
+        </is>
+      </c>
+      <c r="P121" s="2" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>1114</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>MÁSCARA DE PROTEÇÃO DESCARTÁVEL - USO CONFORME RISCO/ATIVIDADE.</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>46.412.993/0001-00</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="n"/>
+      <c r="I122" s="3" t="inlineStr">
+        <is>
+          <t>Máscara Descartável Libus PFF-2 1420 CA N°39051</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="n"/>
+      <c r="K122" s="2" t="n"/>
+      <c r="L122" s="2" t="n"/>
+      <c r="M122" s="2" t="n"/>
+      <c r="N122" s="2" t="n"/>
+      <c r="O122" s="3" t="inlineStr">
+        <is>
+          <t>Preço não exibido (motivo não identificado)</t>
+        </is>
+      </c>
+      <c r="P122" s="4" t="inlineStr">
+        <is>
+          <t>https://www.supriflex.com.br/mascara-respirador-descartavel-pff-2-1420-1420-n95-ca-n39051</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>1117</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>CAPA DE CHUVA - PVC IMPERMEÁVEL, COM CAPUZ E COSTURAS SELADAS.</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>BHZ EPI DISTRIBUIDORA LTDA</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>31.893.116/0001-20</t>
+        </is>
+      </c>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t>https://www.loja.bhzepi.com.br/produto/capa-de-chuva-pvc-amarelo-forrado-tamanho-g.html</t>
+        </is>
+      </c>
+      <c r="I123" s="3" t="inlineStr">
+        <is>
+          <t>Capa De Chuva Pvc Amarelo Forrado Tamanho G</t>
+        </is>
+      </c>
+      <c r="J123" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="K123" s="2" t="n"/>
+      <c r="L123" s="2" t="n"/>
+      <c r="M123" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="N123" s="5" t="n">
+        <v>20.62</v>
+      </c>
+      <c r="O123" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 20,62 7 dias úteis PAC</t>
+        </is>
+      </c>
+      <c r="P123" s="2" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>1117</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>CAPA DE CHUVA - PVC IMPERMEÁVEL, COM CAPUZ E COSTURAS SELADAS.</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>SEGURANCA TOTAL EPIS LTDA</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>39.268.527/0001-37</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>https://www.segurancatotal.com.br/produto/capa-de-chuva-policap-pvc-forrado-azul.html</t>
+        </is>
+      </c>
+      <c r="I124" s="3" t="inlineStr">
+        <is>
+          <t>Capa de Chuva Policap PVC Forrado Azul (Tamanho: M)</t>
+        </is>
+      </c>
+      <c r="J124" s="5" t="n">
+        <v>36.99</v>
+      </c>
+      <c r="K124" s="2" t="n"/>
+      <c r="L124" s="2" t="n"/>
+      <c r="M124" s="5" t="n">
+        <v>36.99</v>
+      </c>
+      <c r="N124" s="5" t="n">
+        <v>20.44</v>
+      </c>
+      <c r="O124" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 20,44 7 dias úteis PAC</t>
+        </is>
+      </c>
+      <c r="P124" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P102"/>
+  <autoFilter ref="A1:P124"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
@@ -6942,6 +8310,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P101" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId123"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
